--- a/hardware/devBoard/manufacture/devBoard BOM.xlsx
+++ b/hardware/devBoard/manufacture/devBoard BOM.xlsx
@@ -5,21 +5,22 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\Documents\GitHub\Embedded-Systems-Instructor\Manufacturing Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\Documents\GitHub\Embedded-Systems-Instructor\hardware\devBoard\manufacture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E30708B4-5213-4634-A94C-BBC06345EABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF451763-B87C-4524-A940-B881E3C96296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="1404" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Digikey" sheetId="4" r:id="rId1"/>
+    <sheet name="Inclusive" sheetId="4" r:id="rId1"/>
     <sheet name="JLCPCB" sheetId="5" r:id="rId2"/>
+    <sheet name="LCSC Part#" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="description" localSheetId="0">Digikey!$E$42</definedName>
-    <definedName name="distributors" localSheetId="0">Digikey!$E$278</definedName>
-    <definedName name="learn" localSheetId="0">Digikey!$E$70</definedName>
+    <definedName name="description" localSheetId="0">Inclusive!$E$42</definedName>
+    <definedName name="distributors" localSheetId="0">Inclusive!$E$278</definedName>
+    <definedName name="learn" localSheetId="0">Inclusive!$E$70</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="225">
   <si>
     <t>A31727CT-ND</t>
   </si>
@@ -591,6 +592,132 @@
   </si>
   <si>
     <t>Footprint</t>
+  </si>
+  <si>
+    <t>Part</t>
+  </si>
+  <si>
+    <t>1206R</t>
+  </si>
+  <si>
+    <t>C2907445</t>
+  </si>
+  <si>
+    <t>C25379</t>
+  </si>
+  <si>
+    <t>C17901</t>
+  </si>
+  <si>
+    <t>C17887</t>
+  </si>
+  <si>
+    <t>C2930433</t>
+  </si>
+  <si>
+    <t>C17948</t>
+  </si>
+  <si>
+    <t>C17902</t>
+  </si>
+  <si>
+    <t>C17927</t>
+  </si>
+  <si>
+    <t>1206C</t>
+  </si>
+  <si>
+    <t>C5137553</t>
+  </si>
+  <si>
+    <t>C24497</t>
+  </si>
+  <si>
+    <t>C1848</t>
+  </si>
+  <si>
+    <t>C13585</t>
+  </si>
+  <si>
+    <t>5.2*5.2</t>
+  </si>
+  <si>
+    <t>C5342990</t>
+  </si>
+  <si>
+    <t>USB</t>
+  </si>
+  <si>
+    <t>C91144</t>
+  </si>
+  <si>
+    <t>SSOP-28</t>
+  </si>
+  <si>
+    <t>C51680</t>
+  </si>
+  <si>
+    <t>SSOP-16</t>
+  </si>
+  <si>
+    <t>C69082</t>
+  </si>
+  <si>
+    <t>C131974</t>
+  </si>
+  <si>
+    <t>C50754</t>
+  </si>
+  <si>
+    <t>SOIC-8</t>
+  </si>
+  <si>
+    <t>C2860743</t>
+  </si>
+  <si>
+    <t>1206D</t>
+  </si>
+  <si>
+    <t>C2984261</t>
+  </si>
+  <si>
+    <t>PLCC-4</t>
+  </si>
+  <si>
+    <t>C5355897</t>
+  </si>
+  <si>
+    <t>C962159</t>
+  </si>
+  <si>
+    <t>JLC Part #</t>
+  </si>
+  <si>
+    <t>LCSC Part #</t>
+  </si>
+  <si>
+    <t>C455262</t>
+  </si>
+  <si>
+    <t>C7494970</t>
+  </si>
+  <si>
+    <t>C2764887</t>
+  </si>
+  <si>
+    <t>C434442 </t>
+  </si>
+  <si>
+    <t>C2898686</t>
+  </si>
+  <si>
+    <t>C375458</t>
+  </si>
+  <si>
+    <t>C51118</t>
+  </si>
+  <si>
+    <t>C142747</t>
   </si>
 </sst>
 </file>
@@ -600,7 +727,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -625,6 +752,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -646,17 +782,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="40">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1188,6 +1326,88 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
         <scheme val="none"/>
@@ -1461,13 +1681,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A2:L38" headerRowCount="0" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Description" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Column3" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Manf" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Manf Part #" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="DigiKey Part #" headerRowDxfId="25" dataDxfId="24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A2:N38" headerRowCount="0" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Description" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Column3" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Manf" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Manf Part #" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="DigiKey Part #" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="14" xr3:uid="{35BB96B2-36D7-4209-B8F8-5562FE5CE59C}" name="Column5" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="13" xr3:uid="{C12B1CAA-091C-4545-9EA9-45AB59751B9E}" name="Column4" headerRowDxfId="25" dataDxfId="24"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Foot" headerRowDxfId="23" dataDxfId="22"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Unit Cost" headerRowDxfId="21" dataDxfId="20"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Per Qty" headerRowDxfId="19" dataDxfId="18"/>
@@ -1485,11 +1707,11 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{076EB5AE-F24E-44AE-8E44-A08FA2D22AEF}" name="Table13" displayName="Table13" ref="A2:C38" headerRowCount="0" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8ADD3722-4744-45B7-AAC2-EEF6E5F4E235}" name="Table134" displayName="Table134" ref="A2:C30" headerRowCount="0" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B81E86A7-3DB6-4ABD-8666-7493DA3A2584}" name="Description" headerRowDxfId="7" dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{F1C4698A-9D06-4292-99BD-464EF0C73221}" name="Column3" headerRowDxfId="5" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{BD37C5AE-7F0C-4707-BC62-9CD534B9D6B5}" name="Foot" headerRowDxfId="3" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{602D18BC-E79A-4163-B949-6F6770052923}" name="Description" headerRowDxfId="7" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{F735619E-9092-4B27-AE29-7EA4CBFA4D20}" name="Column3" headerRowDxfId="5" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{9FCD173A-5CC7-4FDF-A725-E4790DF3492F}" name="Foot" headerRowDxfId="3" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1819,21 +2041,23 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="1"/>
-    <col min="7" max="7" width="9.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.109375" style="1"/>
-    <col min="9" max="9" width="9.44140625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="1"/>
+    <col min="9" max="9" width="9.6640625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="9.109375" style="1"/>
+    <col min="11" max="11" width="9.44140625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>124</v>
       </c>
@@ -1850,26 +2074,32 @@
         <v>168</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>80</v>
       </c>
@@ -1886,28 +2116,31 @@
         <v>63</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="4">
+      <c r="I2" s="4">
         <v>4.9200000000000001E-2</v>
       </c>
-      <c r="H2" s="3">
+      <c r="J2" s="3">
         <v>2</v>
       </c>
-      <c r="I2" s="1">
-        <v>1</v>
-      </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="3">
+      <c r="K2" s="1">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>2</v>
       </c>
-      <c r="L2" s="3">
+      <c r="N2" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>81</v>
       </c>
@@ -1924,28 +2157,32 @@
         <v>39</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="4">
+      <c r="I3" s="4">
         <v>2.6599999999999999E-2</v>
       </c>
-      <c r="H3" s="3">
+      <c r="J3" s="3">
         <v>3</v>
       </c>
-      <c r="I3" s="1">
-        <v>1</v>
-      </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="3">
+      <c r="K3" s="1">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1"/>
+      <c r="M3" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>3</v>
       </c>
-      <c r="L3" s="3">
+      <c r="N3" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>82</v>
       </c>
@@ -1962,28 +2199,32 @@
         <v>40</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="4">
+      <c r="I4" s="4">
         <v>2.6599999999999999E-2</v>
       </c>
-      <c r="H4" s="3">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1</v>
-      </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="3">
+      <c r="J4" s="3">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1"/>
+      <c r="M4" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>1</v>
       </c>
-      <c r="L4" s="3">
+      <c r="N4" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>83</v>
       </c>
@@ -2000,28 +2241,31 @@
         <v>42</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="4">
+      <c r="I5" s="4">
         <v>2.6599999999999999E-2</v>
       </c>
-      <c r="H5" s="3">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="3">
+      <c r="J5" s="3">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1"/>
+      <c r="M5" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>1</v>
       </c>
-      <c r="L5" s="3">
+      <c r="N5" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>84</v>
       </c>
@@ -2038,28 +2282,32 @@
         <v>52</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="4">
+      <c r="I6" s="4">
         <v>2.6599999999999999E-2</v>
       </c>
-      <c r="H6" s="3">
+      <c r="J6" s="3">
         <v>3</v>
       </c>
-      <c r="I6" s="1">
-        <v>1</v>
-      </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="3">
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1"/>
+      <c r="M6" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>3</v>
       </c>
-      <c r="L6" s="3">
+      <c r="N6" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>85</v>
       </c>
@@ -2076,28 +2324,31 @@
         <v>60</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>3.4099999999999998E-2</v>
       </c>
-      <c r="H7" s="3">
+      <c r="J7" s="3">
         <v>3</v>
       </c>
-      <c r="I7" s="1">
-        <v>1</v>
-      </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="3">
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1"/>
+      <c r="M7" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>3</v>
       </c>
-      <c r="L7" s="3">
+      <c r="N7" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>86</v>
       </c>
@@ -2114,28 +2365,31 @@
         <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="4">
+      <c r="I8" s="4">
         <v>2.81E-2</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>8</v>
       </c>
-      <c r="I8" s="1">
-        <v>1</v>
-      </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="3">
+      <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1"/>
+      <c r="M8" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>8</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>87</v>
       </c>
@@ -2151,42 +2405,45 @@
       <c r="E9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="2">
+      <c r="I9" s="2">
         <v>2.6599999999999999E-2</v>
       </c>
-      <c r="H9" s="1">
-        <v>1</v>
-      </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>1</v>
       </c>
       <c r="K9" s="1">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>1</v>
       </c>
-      <c r="L9" s="1">
+      <c r="N9" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D10" s="1"/>
-      <c r="G10" s="4"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="3">
+      <c r="I10" s="4"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>0</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>88</v>
       </c>
@@ -2203,28 +2460,32 @@
         <v>4</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="4">
+      <c r="I11" s="4">
         <v>0.33150000000000002</v>
       </c>
-      <c r="H11" s="3">
-        <v>1</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1</v>
-      </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="3">
+      <c r="J11" s="3">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1"/>
+      <c r="M11" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>1</v>
       </c>
-      <c r="L11" s="3">
+      <c r="N11" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>89</v>
       </c>
@@ -2240,28 +2501,31 @@
       <c r="E12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="2">
+      <c r="I12" s="2">
         <v>6.4399999999999999E-2</v>
       </c>
-      <c r="H12" s="1">
+      <c r="J12" s="1">
         <v>3</v>
       </c>
-      <c r="I12" s="1">
-        <v>1</v>
-      </c>
       <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>3</v>
       </c>
-      <c r="L12" s="1">
+      <c r="N12" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>90</v>
       </c>
@@ -2277,29 +2541,33 @@
       <c r="E13" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="4">
+      <c r="I13" s="4">
         <v>3.2719999999999999E-2</v>
       </c>
-      <c r="H13" s="3">
+      <c r="J13" s="3">
         <v>7</v>
       </c>
-      <c r="I13" s="1">
-        <v>1</v>
-      </c>
-      <c r="J13" s="1"/>
-      <c r="K13" s="3">
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1"/>
+      <c r="M13" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>7</v>
       </c>
-      <c r="L13" s="3">
+      <c r="N13" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>91</v>
       </c>
@@ -2316,28 +2584,31 @@
         <v>108</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="4">
+      <c r="I14" s="4">
         <v>5.3400000000000003E-2</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>3</v>
       </c>
-      <c r="I14" s="1">
-        <v>1</v>
-      </c>
-      <c r="J14" s="1"/>
-      <c r="K14" s="3">
+      <c r="K14" s="1">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1"/>
+      <c r="M14" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>92</v>
       </c>
@@ -2354,38 +2625,41 @@
         <v>120</v>
       </c>
       <c r="F15" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="4">
+      <c r="I15" s="4">
         <v>5.1299999999999998E-2</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>4</v>
       </c>
-      <c r="I15" s="1">
-        <v>1</v>
-      </c>
-      <c r="J15" s="1"/>
-      <c r="K15" s="3">
+      <c r="K15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1"/>
+      <c r="M15" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>4</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K16" s="1">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M16" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>0</v>
       </c>
-      <c r="L16" s="1">
+      <c r="N16" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>125</v>
       </c>
@@ -2401,29 +2675,29 @@
       <c r="E17" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="4">
+      <c r="I17" s="4">
         <v>0.77749999999999997</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4</v>
       </c>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1">
-        <v>1</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="K17" s="1"/>
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
+      <c r="M17" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>0</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>126</v>
       </c>
@@ -2439,29 +2713,29 @@
       <c r="E18" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G18" s="4">
+      <c r="I18" s="4">
         <v>0.77749999999999997</v>
       </c>
-      <c r="H18" s="3">
-        <v>1</v>
-      </c>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1">
-        <v>1</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="J18" s="3">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
+      <c r="M18" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>0</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>128</v>
       </c>
@@ -2477,29 +2751,29 @@
       <c r="E19" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="4">
+      <c r="I19" s="4">
         <v>0.74</v>
       </c>
-      <c r="H19" s="3">
+      <c r="J19" s="3">
         <v>2</v>
       </c>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1">
-        <v>1</v>
-      </c>
-      <c r="K19" s="3">
+      <c r="K19" s="1"/>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
+      <c r="M19" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>0</v>
       </c>
-      <c r="L19" s="3">
+      <c r="N19" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>93</v>
       </c>
@@ -2515,29 +2789,29 @@
       <c r="E20" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G20" s="4">
+      <c r="I20" s="4">
         <v>1.137</v>
       </c>
-      <c r="H20" s="3">
-        <v>1</v>
-      </c>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1">
-        <v>1</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="J20" s="3">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
+      <c r="M20" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>0</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>94</v>
       </c>
@@ -2553,29 +2827,33 @@
       <c r="E21" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="4">
+      <c r="I21" s="4">
         <v>1.4039999999999999</v>
       </c>
-      <c r="H21" s="3">
-        <v>1</v>
-      </c>
-      <c r="I21" s="1">
-        <v>1</v>
-      </c>
-      <c r="J21" s="1"/>
-      <c r="K21" s="3">
+      <c r="J21" s="3">
+        <v>1</v>
+      </c>
+      <c r="K21" s="1">
+        <v>1</v>
+      </c>
+      <c r="L21" s="1"/>
+      <c r="M21" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>1</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>95</v>
       </c>
@@ -2591,29 +2869,31 @@
       <c r="E22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G22" s="4">
+      <c r="I22" s="4">
         <v>0.35770000000000002</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>2</v>
       </c>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1">
-        <v>1</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="K22" s="1"/>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
+      <c r="M22" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>0</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>110</v>
       </c>
@@ -2630,28 +2910,34 @@
         <v>113</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G23" t="s">
+        <v>217</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="4">
+      <c r="I23" s="4">
         <v>8.2400000000000001E-2</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>3</v>
       </c>
-      <c r="I23" s="1">
-        <v>1</v>
-      </c>
-      <c r="J23" s="1"/>
-      <c r="K23" s="3">
+      <c r="K23" s="1">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1"/>
+      <c r="M23" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>3</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>96</v>
       </c>
@@ -2667,29 +2953,29 @@
       <c r="E24" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G24" s="4">
+      <c r="I24" s="4">
         <v>0.52900000000000003</v>
       </c>
-      <c r="H24" s="3">
-        <v>1</v>
-      </c>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1">
-        <v>1</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="J24" s="3">
+        <v>1</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
+      <c r="M24" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>0</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>97</v>
       </c>
@@ -2705,38 +2991,38 @@
       <c r="E25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="2">
+      <c r="I25" s="2">
         <v>1.4718</v>
       </c>
-      <c r="H25" s="1">
-        <v>1</v>
-      </c>
       <c r="J25" s="1">
         <v>1</v>
       </c>
-      <c r="K25" s="1">
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
+      <c r="M25" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>0</v>
       </c>
-      <c r="L25" s="1">
+      <c r="N25" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K26" s="1">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M26" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>0</v>
       </c>
-      <c r="L26" s="1">
+      <c r="N26" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>177</v>
       </c>
@@ -2752,28 +3038,31 @@
       <c r="E27" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G27" s="4">
+      <c r="I27" s="4">
         <v>2.1800000000000002</v>
       </c>
-      <c r="H27" s="3">
-        <v>1</v>
-      </c>
-      <c r="I27" s="1">
+      <c r="J27" s="3">
         <v>1</v>
       </c>
       <c r="K27" s="1">
+        <v>1</v>
+      </c>
+      <c r="M27" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>1</v>
       </c>
-      <c r="L27" s="1">
+      <c r="N27" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>98</v>
       </c>
@@ -2790,28 +3079,31 @@
         <v>57</v>
       </c>
       <c r="F28" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G28" s="4">
+      <c r="I28" s="4">
         <v>1.9</v>
       </c>
-      <c r="H28" s="3">
-        <v>1</v>
-      </c>
-      <c r="I28" s="1">
-        <v>1</v>
-      </c>
-      <c r="J28" s="1"/>
-      <c r="K28" s="3">
+      <c r="J28" s="3">
+        <v>1</v>
+      </c>
+      <c r="K28" s="1">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1"/>
+      <c r="M28" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>1</v>
       </c>
-      <c r="L28" s="3">
+      <c r="N28" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>99</v>
       </c>
@@ -2828,28 +3120,34 @@
         <v>9</v>
       </c>
       <c r="F29" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G29" t="s">
+        <v>206</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G29" s="4">
+      <c r="I29" s="4">
         <v>1.048</v>
       </c>
-      <c r="H29" s="3">
+      <c r="J29" s="3">
         <v>2</v>
       </c>
-      <c r="I29" s="1">
-        <v>1</v>
-      </c>
-      <c r="J29" s="1"/>
-      <c r="K29" s="3">
+      <c r="K29" s="1">
+        <v>1</v>
+      </c>
+      <c r="L29" s="1"/>
+      <c r="M29" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>2</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>100</v>
       </c>
@@ -2865,28 +3163,34 @@
       <c r="E30" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" t="s">
+        <v>221</v>
+      </c>
+      <c r="G30" t="s">
+        <v>221</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G30" s="2">
+      <c r="I30" s="2">
         <v>0.05</v>
       </c>
-      <c r="H30" s="1">
-        <v>1</v>
-      </c>
-      <c r="I30" s="1">
+      <c r="J30" s="1">
         <v>1</v>
       </c>
       <c r="K30" s="1">
+        <v>1</v>
+      </c>
+      <c r="M30" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>1</v>
       </c>
-      <c r="L30" s="1">
+      <c r="N30" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>117</v>
       </c>
@@ -2903,27 +3207,33 @@
         <v>115</v>
       </c>
       <c r="F31" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="G31" t="s">
+        <v>223</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G31" s="2">
+      <c r="I31" s="2">
         <v>0.41</v>
       </c>
-      <c r="H31" s="1">
-        <v>1</v>
-      </c>
-      <c r="I31" s="1">
+      <c r="J31" s="1">
         <v>1</v>
       </c>
       <c r="K31" s="1">
+        <v>1</v>
+      </c>
+      <c r="M31" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>1</v>
       </c>
-      <c r="L31" s="1">
+      <c r="N31" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>101</v>
       </c>
@@ -2939,28 +3249,34 @@
       <c r="E32" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G32" t="s">
+        <v>218</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G32" s="4">
+      <c r="I32" s="4">
         <v>0.83209999999999995</v>
       </c>
-      <c r="H32" s="3">
-        <v>1</v>
-      </c>
-      <c r="I32" s="1">
+      <c r="J32" s="3">
         <v>1</v>
       </c>
       <c r="K32" s="1">
+        <v>1</v>
+      </c>
+      <c r="M32" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>1</v>
       </c>
-      <c r="L32" s="1">
+      <c r="N32" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>102</v>
       </c>
@@ -2976,29 +3292,33 @@
       <c r="E33" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G33" s="2">
+      <c r="I33" s="2">
         <v>0.70399999999999996</v>
       </c>
-      <c r="H33" s="3">
-        <v>1</v>
-      </c>
-      <c r="I33" s="1">
-        <v>1</v>
-      </c>
-      <c r="J33" s="1"/>
-      <c r="K33" s="3">
+      <c r="J33" s="3">
+        <v>1</v>
+      </c>
+      <c r="K33" s="1">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1"/>
+      <c r="M33" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>1</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>103</v>
       </c>
@@ -3014,29 +3334,35 @@
       <c r="E34" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" t="s">
+        <v>220</v>
+      </c>
+      <c r="G34" t="s">
+        <v>220</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G34" s="4">
+      <c r="I34" s="4">
         <v>0.1085</v>
       </c>
-      <c r="H34" s="3">
-        <v>1</v>
-      </c>
-      <c r="I34" s="1">
-        <v>1</v>
-      </c>
-      <c r="J34" s="1"/>
-      <c r="K34" s="3">
+      <c r="J34" s="3">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1"/>
+      <c r="M34" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>1</v>
       </c>
-      <c r="L34" s="3">
+      <c r="N34" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>104</v>
       </c>
@@ -3052,29 +3378,35 @@
       <c r="E35" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" t="s">
+        <v>222</v>
+      </c>
+      <c r="G35" t="s">
+        <v>222</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G35" s="4">
+      <c r="I35" s="4">
         <v>0.12189999999999999</v>
       </c>
-      <c r="H35" s="3">
-        <v>1</v>
-      </c>
-      <c r="I35" s="1">
-        <v>1</v>
-      </c>
-      <c r="J35" s="1"/>
-      <c r="K35" s="3">
+      <c r="J35" s="3">
+        <v>1</v>
+      </c>
+      <c r="K35" s="1">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1"/>
+      <c r="M35" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>1</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>105</v>
       </c>
@@ -3090,29 +3422,35 @@
       <c r="E36" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G36" t="s">
+        <v>219</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G36" s="4">
+      <c r="I36" s="4">
         <v>0.37430000000000002</v>
       </c>
-      <c r="H36" s="3">
-        <v>1</v>
-      </c>
-      <c r="I36" s="1">
-        <v>1</v>
-      </c>
-      <c r="J36" s="1"/>
-      <c r="K36" s="3">
+      <c r="J36" s="3">
+        <v>1</v>
+      </c>
+      <c r="K36" s="1">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1"/>
+      <c r="M36" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>1</v>
       </c>
-      <c r="L36" s="3">
+      <c r="N36" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>106</v>
       </c>
@@ -3128,28 +3466,34 @@
       <c r="E37" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G37" t="s">
+        <v>213</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G37" s="4">
+      <c r="I37" s="4">
         <v>0.36480000000000001</v>
       </c>
-      <c r="H37" s="3">
-        <v>1</v>
-      </c>
-      <c r="I37" s="1">
+      <c r="J37" s="3">
         <v>1</v>
       </c>
       <c r="K37" s="1">
+        <v>1</v>
+      </c>
+      <c r="M37" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>1</v>
       </c>
-      <c r="L37" s="1">
+      <c r="N37" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>107</v>
       </c>
@@ -3165,43 +3509,43 @@
       <c r="E38" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="H38" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>0.8639</v>
       </c>
-      <c r="H38" s="1">
-        <v>1</v>
-      </c>
-      <c r="I38" s="1">
+      <c r="J38" s="1">
         <v>1</v>
       </c>
       <c r="K38" s="1">
+        <v>1</v>
+      </c>
+      <c r="M38" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>1</v>
       </c>
-      <c r="L38" s="1">
+      <c r="N38" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3">
         <f>COUNTA(Table1[Manf])</f>
         <v>34</v>
       </c>
-      <c r="H41" s="1">
+      <c r="J41" s="1">
         <f>SUM(Table1[Per Qty])</f>
         <v>69</v>
       </c>
-      <c r="K41" s="1">
+      <c r="M41" s="1">
         <f>SUM(Table1[Column1])</f>
         <v>57</v>
       </c>
-      <c r="L41" s="1">
+      <c r="N41" s="1">
         <f>SUM(Table1[Column2])</f>
         <v>12</v>
       </c>
@@ -3229,14 +3573,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECAE32E7-7895-42B0-B9C6-999EBEE1184D}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26.109375" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>181</v>
       </c>
@@ -3246,8 +3590,11 @@
       <c r="C1" s="1" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>80</v>
       </c>
@@ -3255,10 +3602,14 @@
         <v>137</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+      <c r="D2" s="3" t="str">
+        <f>Table1[[#This Row],[Column5]]</f>
+        <v>C2907445</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>81</v>
       </c>
@@ -3266,10 +3617,14 @@
         <v>141</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <f>Table1[[#This Row],[Column5]]</f>
+        <v>C25379</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>82</v>
       </c>
@@ -3277,10 +3632,14 @@
         <v>132</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+      <c r="D4" s="3" t="str">
+        <f>Table1[[#This Row],[Column5]]</f>
+        <v>C17901</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>83</v>
       </c>
@@ -3288,10 +3647,14 @@
         <v>140</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+      <c r="D5" s="3" t="str">
+        <f>Table1[[#This Row],[Column5]]</f>
+        <v>C17887</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>84</v>
       </c>
@@ -3299,10 +3662,14 @@
         <v>144</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+      <c r="D6" s="3" t="str">
+        <f>Table1[[#This Row],[Column5]]</f>
+        <v>C2930433</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>85</v>
       </c>
@@ -3310,10 +3677,14 @@
         <v>138</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+      <c r="D7" s="3" t="str">
+        <f>Table1[[#This Row],[Column5]]</f>
+        <v>C17948</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>86</v>
       </c>
@@ -3321,10 +3692,14 @@
         <v>133</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+      <c r="D8" s="3" t="str">
+        <f>Table1[[#This Row],[Column5]]</f>
+        <v>C17902</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>87</v>
       </c>
@@ -3332,11 +3707,15 @@
         <v>135</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+      <c r="D9" s="3" t="str">
+        <f>Table1[[#This Row],[Column5]]</f>
+        <v>C17927</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>88</v>
       </c>
@@ -3344,10 +3723,14 @@
         <v>143</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+      <c r="D11" s="3" t="str">
+        <f>Table1[[#This Row],[Column5]]</f>
+        <v>C142747</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>89</v>
       </c>
@@ -3355,21 +3738,29 @@
         <v>142</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+      <c r="D12" s="3" t="str">
+        <f>Table1[[#This Row],[Column5]]</f>
+        <v>C5137553</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>90</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D13" s="3" t="str">
+        <f>Table1[[#This Row],[Column5]]</f>
+        <v>C24497</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>91</v>
       </c>
@@ -3377,10 +3768,14 @@
         <v>136</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+      <c r="D14" s="3" t="str">
+        <f>Table1[[#This Row],[Column5]]</f>
+        <v>C1848</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>92</v>
       </c>
@@ -3388,246 +3783,216 @@
         <v>134</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+      <c r="D15" s="3" t="str">
+        <f>Table1[[#This Row],[Column5]]</f>
+        <v>C13585</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C17" t="s">
+        <v>198</v>
+      </c>
+      <c r="D17" s="1" t="str">
+        <f>Inclusive!F23</f>
+        <v>C5342990</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1" t="str">
+        <f>Inclusive!F21</f>
+        <v>C91144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>160</v>
+        <v>177</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="D20" s="1" t="str">
+        <f>Inclusive!F27</f>
+        <v>C51680</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+      <c r="D21" s="1" t="str">
+        <f>Inclusive!F28</f>
+        <v>C69082</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>130</v>
+        <v>99</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>110</v>
+        <v>26</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>Inclusive!F29</f>
+        <v>C131974</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="D23" s="1" t="str">
+        <f>Inclusive!F30</f>
+        <v>C2898686</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>97</v>
+        <v>117</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="1" t="str">
+        <f>Inclusive!F31</f>
+        <v>C50754</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D25" s="1" t="str">
+        <f>Inclusive!F32</f>
+        <v>C2860743</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D26" s="1" t="str">
+        <f>Inclusive!F33</f>
+        <v>C2984261</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+      <c r="D27" s="1" t="str">
+        <f>Inclusive!F34</f>
+        <v>C434442 </v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+      <c r="D29" s="1" t="str">
+        <f>Inclusive!F36</f>
+        <v>C5355897</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C38" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
+      <c r="D30" s="1" t="str">
+        <f>Inclusive!F37</f>
+        <v>C962159</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A38">
+  <conditionalFormatting sqref="A2:A30">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="DONE">
       <formula>NOT(ISERROR(SEARCH("DONE",A2)))</formula>
     </cfRule>
@@ -3637,4 +4002,13 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EACDD468-810C-4EBE-B830-FE01E4A2676D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/hardware/devBoard/manufacture/devBoard BOM.xlsx
+++ b/hardware/devBoard/manufacture/devBoard BOM.xlsx
@@ -5,36 +5,23 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\Documents\GitHub\Embedded-Systems-Instructor\hardware\devBoard\manufacture\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Documents\GitHub\Embedded-Systems-Instructor\hardware\devBoard\manufacture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF451763-B87C-4524-A940-B881E3C96296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A506DC-CA71-4A10-BD86-88E0336A8564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Inclusive" sheetId="4" r:id="rId1"/>
-    <sheet name="JLCPCB" sheetId="5" r:id="rId2"/>
-    <sheet name="LCSC Part#" sheetId="6" r:id="rId3"/>
+    <sheet name="devBoard BOM" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="description" localSheetId="0">Inclusive!$E$42</definedName>
-    <definedName name="distributors" localSheetId="0">Inclusive!$E$278</definedName>
-    <definedName name="learn" localSheetId="0">Inclusive!$E$70</definedName>
+    <definedName name="description" localSheetId="0">'devBoard BOM'!$E$42</definedName>
+    <definedName name="distributors" localSheetId="0">'devBoard BOM'!$E$278</definedName>
+    <definedName name="learn" localSheetId="0">'devBoard BOM'!$E$70</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -43,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="181">
   <si>
     <t>A31727CT-ND</t>
   </si>
@@ -586,138 +573,6 @@
   </si>
   <si>
     <t>PIC18F25K22-I/SS-ND</t>
-  </si>
-  <si>
-    <t>Comment</t>
-  </si>
-  <si>
-    <t>Footprint</t>
-  </si>
-  <si>
-    <t>Part</t>
-  </si>
-  <si>
-    <t>1206R</t>
-  </si>
-  <si>
-    <t>C2907445</t>
-  </si>
-  <si>
-    <t>C25379</t>
-  </si>
-  <si>
-    <t>C17901</t>
-  </si>
-  <si>
-    <t>C17887</t>
-  </si>
-  <si>
-    <t>C2930433</t>
-  </si>
-  <si>
-    <t>C17948</t>
-  </si>
-  <si>
-    <t>C17902</t>
-  </si>
-  <si>
-    <t>C17927</t>
-  </si>
-  <si>
-    <t>1206C</t>
-  </si>
-  <si>
-    <t>C5137553</t>
-  </si>
-  <si>
-    <t>C24497</t>
-  </si>
-  <si>
-    <t>C1848</t>
-  </si>
-  <si>
-    <t>C13585</t>
-  </si>
-  <si>
-    <t>5.2*5.2</t>
-  </si>
-  <si>
-    <t>C5342990</t>
-  </si>
-  <si>
-    <t>USB</t>
-  </si>
-  <si>
-    <t>C91144</t>
-  </si>
-  <si>
-    <t>SSOP-28</t>
-  </si>
-  <si>
-    <t>C51680</t>
-  </si>
-  <si>
-    <t>SSOP-16</t>
-  </si>
-  <si>
-    <t>C69082</t>
-  </si>
-  <si>
-    <t>C131974</t>
-  </si>
-  <si>
-    <t>C50754</t>
-  </si>
-  <si>
-    <t>SOIC-8</t>
-  </si>
-  <si>
-    <t>C2860743</t>
-  </si>
-  <si>
-    <t>1206D</t>
-  </si>
-  <si>
-    <t>C2984261</t>
-  </si>
-  <si>
-    <t>PLCC-4</t>
-  </si>
-  <si>
-    <t>C5355897</t>
-  </si>
-  <si>
-    <t>C962159</t>
-  </si>
-  <si>
-    <t>JLC Part #</t>
-  </si>
-  <si>
-    <t>LCSC Part #</t>
-  </si>
-  <si>
-    <t>C455262</t>
-  </si>
-  <si>
-    <t>C7494970</t>
-  </si>
-  <si>
-    <t>C2764887</t>
-  </si>
-  <si>
-    <t>C434442 </t>
-  </si>
-  <si>
-    <t>C2898686</t>
-  </si>
-  <si>
-    <t>C375458</t>
-  </si>
-  <si>
-    <t>C51118</t>
-  </si>
-  <si>
-    <t>C142747</t>
   </si>
 </sst>
 </file>
@@ -727,7 +582,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -752,15 +607,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -782,19 +628,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="27">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -802,195 +646,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1326,88 +981,6 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
         <scheme val="none"/>
@@ -1681,37 +1254,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A2:N38" headerRowCount="0" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
-  <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Description" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Column3" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Manf" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Manf Part #" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="DigiKey Part #" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="14" xr3:uid="{35BB96B2-36D7-4209-B8F8-5562FE5CE59C}" name="Column5" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="13" xr3:uid="{C12B1CAA-091C-4545-9EA9-45AB59751B9E}" name="Column4" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Foot" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Unit Cost" headerRowDxfId="21" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Per Qty" headerRowDxfId="19" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="SMT" headerRowDxfId="17" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Through" headerRowDxfId="15" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Column1" headerRowDxfId="13" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A2:L38" headerRowCount="0" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Description" headerRowDxfId="24" dataDxfId="23"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Column3" headerRowDxfId="22" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Manf" headerRowDxfId="20" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Manf Part #" headerRowDxfId="18" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="DigiKey Part #" headerRowDxfId="16" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Foot" headerRowDxfId="14" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Unit Cost" headerRowDxfId="12" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Per Qty" headerRowDxfId="10" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="SMT" headerRowDxfId="8" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Through" headerRowDxfId="6" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Column1" headerRowDxfId="4" dataDxfId="3">
       <calculatedColumnFormula>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Column2" headerRowDxfId="11" dataDxfId="10">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Column2" headerRowDxfId="2" dataDxfId="1">
       <calculatedColumnFormula>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</calculatedColumnFormula>
     </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8ADD3722-4744-45B7-AAC2-EEF6E5F4E235}" name="Table134" displayName="Table134" ref="A2:C30" headerRowCount="0" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{602D18BC-E79A-4163-B949-6F6770052923}" name="Description" headerRowDxfId="7" dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{F735619E-9092-4B27-AE29-7EA4CBFA4D20}" name="Column3" headerRowDxfId="5" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{9FCD173A-5CC7-4FDF-A725-E4790DF3492F}" name="Foot" headerRowDxfId="3" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2041,23 +1601,21 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="1"/>
+    <col min="7" max="7" width="9.6640625" style="2" customWidth="1"/>
     <col min="8" max="8" width="9.109375" style="1"/>
-    <col min="9" max="9" width="9.6640625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" style="1"/>
-    <col min="11" max="11" width="9.44140625" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.109375" style="1"/>
+    <col min="9" max="9" width="9.44140625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>124</v>
       </c>
@@ -2074,32 +1632,26 @@
         <v>168</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>216</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="1"/>
+        <v>169</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>122</v>
+      </c>
       <c r="J1" s="1" t="s">
-        <v>169</v>
+        <v>123</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="N1" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>80</v>
       </c>
@@ -2116,31 +1668,28 @@
         <v>63</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="4">
+      <c r="G2" s="4">
         <v>4.9200000000000001E-2</v>
       </c>
-      <c r="J2" s="3">
+      <c r="H2" s="3">
         <v>2</v>
       </c>
-      <c r="K2" s="1">
-        <v>1</v>
-      </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="3">
+      <c r="I2" s="1">
+        <v>1</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>2</v>
       </c>
-      <c r="N2" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L2" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>81</v>
       </c>
@@ -2157,32 +1706,28 @@
         <v>39</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="4">
+      <c r="G3" s="4">
         <v>2.6599999999999999E-2</v>
       </c>
-      <c r="J3" s="3">
+      <c r="H3" s="3">
         <v>3</v>
       </c>
-      <c r="K3" s="1">
-        <v>1</v>
-      </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="3">
+      <c r="I3" s="1">
+        <v>1</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>3</v>
       </c>
-      <c r="N3" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L3" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>82</v>
       </c>
@@ -2199,32 +1744,28 @@
         <v>40</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="4">
+      <c r="G4" s="4">
         <v>2.6599999999999999E-2</v>
       </c>
-      <c r="J4" s="3">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1">
-        <v>1</v>
-      </c>
-      <c r="L4" s="1"/>
-      <c r="M4" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>1</v>
-      </c>
-      <c r="N4" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>1</v>
+      </c>
+      <c r="L4" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>83</v>
       </c>
@@ -2241,31 +1782,28 @@
         <v>42</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="4">
+      <c r="G5" s="4">
         <v>2.6599999999999999E-2</v>
       </c>
-      <c r="J5" s="3">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1">
-        <v>1</v>
-      </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>1</v>
-      </c>
-      <c r="N5" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>1</v>
+      </c>
+      <c r="L5" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>84</v>
       </c>
@@ -2282,32 +1820,28 @@
         <v>52</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="4">
+      <c r="G6" s="4">
         <v>2.6599999999999999E-2</v>
       </c>
-      <c r="J6" s="3">
+      <c r="H6" s="3">
         <v>3</v>
       </c>
-      <c r="K6" s="1">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="3">
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>3</v>
       </c>
-      <c r="N6" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L6" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>85</v>
       </c>
@@ -2324,31 +1858,28 @@
         <v>60</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="2">
+      <c r="G7" s="2">
         <v>3.4099999999999998E-2</v>
       </c>
-      <c r="J7" s="3">
+      <c r="H7" s="3">
         <v>3</v>
       </c>
-      <c r="K7" s="1">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1"/>
-      <c r="M7" s="3">
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>3</v>
       </c>
-      <c r="N7" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L7" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>86</v>
       </c>
@@ -2365,31 +1896,28 @@
         <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="4">
+      <c r="G8" s="4">
         <v>2.81E-2</v>
       </c>
-      <c r="J8" s="3">
+      <c r="H8" s="3">
         <v>8</v>
       </c>
-      <c r="K8" s="1">
-        <v>1</v>
-      </c>
-      <c r="L8" s="1"/>
-      <c r="M8" s="3">
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>8</v>
       </c>
-      <c r="N8" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L8" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>87</v>
       </c>
@@ -2405,45 +1933,42 @@
       <c r="E9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="H9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="2">
+      <c r="G9" s="2">
         <v>2.6599999999999999E-2</v>
       </c>
-      <c r="J9" s="1">
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
         <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>1</v>
-      </c>
-      <c r="M9" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>1</v>
-      </c>
-      <c r="N9" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>1</v>
+      </c>
+      <c r="L9" s="1">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D10" s="1"/>
-      <c r="I10" s="4"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>0</v>
-      </c>
-      <c r="N10" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G10" s="4"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>88</v>
       </c>
@@ -2460,32 +1985,28 @@
         <v>4</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="4">
+      <c r="G11" s="4">
         <v>0.33150000000000002</v>
       </c>
-      <c r="J11" s="3">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1">
-        <v>1</v>
-      </c>
-      <c r="L11" s="1"/>
-      <c r="M11" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>1</v>
-      </c>
-      <c r="N11" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>1</v>
+      </c>
+      <c r="L11" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>89</v>
       </c>
@@ -2501,31 +2022,28 @@
       <c r="E12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="2">
+      <c r="G12" s="2">
         <v>6.4399999999999999E-2</v>
       </c>
-      <c r="J12" s="1">
+      <c r="H12" s="1">
         <v>3</v>
       </c>
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
       <c r="K12" s="1">
-        <v>1</v>
-      </c>
-      <c r="M12" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>3</v>
       </c>
-      <c r="N12" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L12" s="1">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>90</v>
       </c>
@@ -2541,33 +2059,29 @@
       <c r="E13" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I13" s="4">
+      <c r="G13" s="4">
         <v>3.2719999999999999E-2</v>
       </c>
-      <c r="J13" s="3">
+      <c r="H13" s="3">
         <v>7</v>
       </c>
-      <c r="K13" s="1">
-        <v>1</v>
-      </c>
-      <c r="L13" s="1"/>
-      <c r="M13" s="3">
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>7</v>
       </c>
-      <c r="N13" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L13" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>91</v>
       </c>
@@ -2584,31 +2098,28 @@
         <v>108</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="H14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I14" s="4">
+      <c r="G14" s="4">
         <v>5.3400000000000003E-2</v>
       </c>
-      <c r="J14" s="3">
+      <c r="H14" s="3">
         <v>3</v>
       </c>
-      <c r="K14" s="1">
-        <v>1</v>
-      </c>
-      <c r="L14" s="1"/>
-      <c r="M14" s="3">
+      <c r="I14" s="1">
+        <v>1</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L14" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>92</v>
       </c>
@@ -2625,41 +2136,38 @@
         <v>120</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="H15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I15" s="4">
+      <c r="G15" s="4">
         <v>5.1299999999999998E-2</v>
       </c>
-      <c r="J15" s="3">
+      <c r="H15" s="3">
         <v>4</v>
       </c>
-      <c r="K15" s="1">
-        <v>1</v>
-      </c>
-      <c r="L15" s="1"/>
-      <c r="M15" s="3">
+      <c r="I15" s="1">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>4</v>
       </c>
-      <c r="N15" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="M16" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L15" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K16" s="1">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>125</v>
       </c>
@@ -2675,29 +2183,29 @@
       <c r="E17" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I17" s="4">
+      <c r="G17" s="4">
         <v>0.77749999999999997</v>
       </c>
-      <c r="J17" s="3">
+      <c r="H17" s="3">
         <v>4</v>
       </c>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1">
-        <v>1</v>
-      </c>
-      <c r="M17" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>0</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="I17" s="1"/>
+      <c r="J17" s="1">
+        <v>1</v>
+      </c>
+      <c r="K17" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>126</v>
       </c>
@@ -2713,29 +2221,29 @@
       <c r="E18" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I18" s="4">
+      <c r="G18" s="4">
         <v>0.77749999999999997</v>
       </c>
-      <c r="J18" s="3">
-        <v>1</v>
-      </c>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1">
-        <v>1</v>
-      </c>
-      <c r="M18" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>0</v>
-      </c>
-      <c r="N18" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H18" s="3">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1">
+        <v>1</v>
+      </c>
+      <c r="K18" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>128</v>
       </c>
@@ -2751,29 +2259,29 @@
       <c r="E19" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I19" s="4">
+      <c r="G19" s="4">
         <v>0.74</v>
       </c>
-      <c r="J19" s="3">
+      <c r="H19" s="3">
         <v>2</v>
       </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1">
-        <v>1</v>
-      </c>
-      <c r="M19" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>0</v>
-      </c>
-      <c r="N19" s="3">
+      <c r="I19" s="1"/>
+      <c r="J19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>93</v>
       </c>
@@ -2789,29 +2297,29 @@
       <c r="E20" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I20" s="4">
+      <c r="G20" s="4">
         <v>1.137</v>
       </c>
-      <c r="J20" s="3">
-        <v>1</v>
-      </c>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1">
-        <v>1</v>
-      </c>
-      <c r="M20" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H20" s="3">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>94</v>
       </c>
@@ -2827,33 +2335,29 @@
       <c r="E21" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I21" s="4">
+      <c r="G21" s="4">
         <v>1.4039999999999999</v>
       </c>
-      <c r="J21" s="3">
-        <v>1</v>
-      </c>
-      <c r="K21" s="1">
-        <v>1</v>
-      </c>
-      <c r="L21" s="1"/>
-      <c r="M21" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>1</v>
-      </c>
-      <c r="N21" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H21" s="3">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1</v>
+      </c>
+      <c r="J21" s="1"/>
+      <c r="K21" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>1</v>
+      </c>
+      <c r="L21" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>95</v>
       </c>
@@ -2869,31 +2373,29 @@
       <c r="E22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I22" s="4">
+      <c r="G22" s="4">
         <v>0.35770000000000002</v>
       </c>
-      <c r="J22" s="3">
+      <c r="H22" s="3">
         <v>2</v>
       </c>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1">
-        <v>1</v>
-      </c>
-      <c r="M22" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="I22" s="1"/>
+      <c r="J22" s="1">
+        <v>1</v>
+      </c>
+      <c r="K22" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:14" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>110</v>
       </c>
@@ -2910,34 +2412,28 @@
         <v>113</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G23" t="s">
-        <v>217</v>
-      </c>
-      <c r="H23" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I23" s="4">
+      <c r="G23" s="4">
         <v>8.2400000000000001E-2</v>
       </c>
-      <c r="J23" s="3">
+      <c r="H23" s="3">
         <v>3</v>
       </c>
-      <c r="K23" s="1">
-        <v>1</v>
-      </c>
-      <c r="L23" s="1"/>
-      <c r="M23" s="3">
+      <c r="I23" s="1">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1"/>
+      <c r="K23" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>3</v>
       </c>
-      <c r="N23" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L23" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>96</v>
       </c>
@@ -2953,29 +2449,29 @@
       <c r="E24" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I24" s="4">
+      <c r="G24" s="4">
         <v>0.52900000000000003</v>
       </c>
-      <c r="J24" s="3">
-        <v>1</v>
-      </c>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1">
-        <v>1</v>
-      </c>
-      <c r="M24" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H24" s="3">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1">
+        <v>1</v>
+      </c>
+      <c r="K24" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>97</v>
       </c>
@@ -2991,38 +2487,38 @@
       <c r="E25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="2">
+      <c r="G25" s="2">
         <v>1.4718</v>
       </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
       <c r="J25" s="1">
         <v>1</v>
       </c>
+      <c r="K25" s="1">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>0</v>
+      </c>
       <c r="L25" s="1">
-        <v>1</v>
-      </c>
-      <c r="M25" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>0</v>
-      </c>
-      <c r="N25" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="M26" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>0</v>
-      </c>
-      <c r="N26" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K26" s="1">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>177</v>
       </c>
@@ -3038,31 +2534,28 @@
       <c r="E27" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="H27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I27" s="4">
+      <c r="G27" s="4">
         <v>2.1800000000000002</v>
       </c>
-      <c r="J27" s="3">
+      <c r="H27" s="3">
+        <v>1</v>
+      </c>
+      <c r="I27" s="1">
         <v>1</v>
       </c>
       <c r="K27" s="1">
-        <v>1</v>
-      </c>
-      <c r="M27" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>1</v>
-      </c>
-      <c r="N27" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>1</v>
+      </c>
+      <c r="L27" s="1">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>98</v>
       </c>
@@ -3079,31 +2572,28 @@
         <v>57</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="H28" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I28" s="4">
+      <c r="G28" s="4">
         <v>1.9</v>
       </c>
-      <c r="J28" s="3">
-        <v>1</v>
-      </c>
-      <c r="K28" s="1">
-        <v>1</v>
-      </c>
-      <c r="L28" s="1"/>
-      <c r="M28" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>1</v>
-      </c>
-      <c r="N28" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H28" s="3">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1">
+        <v>1</v>
+      </c>
+      <c r="J28" s="1"/>
+      <c r="K28" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>1</v>
+      </c>
+      <c r="L28" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>99</v>
       </c>
@@ -3120,34 +2610,28 @@
         <v>9</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G29" t="s">
-        <v>206</v>
-      </c>
-      <c r="H29" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I29" s="4">
+      <c r="G29" s="4">
         <v>1.048</v>
       </c>
-      <c r="J29" s="3">
+      <c r="H29" s="3">
         <v>2</v>
       </c>
-      <c r="K29" s="1">
-        <v>1</v>
-      </c>
-      <c r="L29" s="1"/>
-      <c r="M29" s="3">
+      <c r="I29" s="1">
+        <v>1</v>
+      </c>
+      <c r="J29" s="1"/>
+      <c r="K29" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>2</v>
       </c>
-      <c r="N29" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="L29" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>100</v>
       </c>
@@ -3163,34 +2647,28 @@
       <c r="E30" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F30" t="s">
-        <v>221</v>
-      </c>
-      <c r="G30" t="s">
-        <v>221</v>
-      </c>
-      <c r="H30" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I30" s="2">
+      <c r="G30" s="2">
         <v>0.05</v>
       </c>
-      <c r="J30" s="1">
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1">
         <v>1</v>
       </c>
       <c r="K30" s="1">
-        <v>1</v>
-      </c>
-      <c r="M30" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>1</v>
-      </c>
-      <c r="N30" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>1</v>
+      </c>
+      <c r="L30" s="1">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>117</v>
       </c>
@@ -3207,33 +2685,27 @@
         <v>115</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="G31" t="s">
-        <v>223</v>
-      </c>
-      <c r="H31" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I31" s="2">
+      <c r="G31" s="2">
         <v>0.41</v>
       </c>
-      <c r="J31" s="1">
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
+      <c r="I31" s="1">
         <v>1</v>
       </c>
       <c r="K31" s="1">
-        <v>1</v>
-      </c>
-      <c r="M31" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>1</v>
-      </c>
-      <c r="N31" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>1</v>
+      </c>
+      <c r="L31" s="1">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>101</v>
       </c>
@@ -3249,34 +2721,28 @@
       <c r="E32" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="G32" t="s">
-        <v>218</v>
-      </c>
-      <c r="H32" s="3" t="s">
+      <c r="F32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I32" s="4">
+      <c r="G32" s="4">
         <v>0.83209999999999995</v>
       </c>
-      <c r="J32" s="3">
+      <c r="H32" s="3">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1">
         <v>1</v>
       </c>
       <c r="K32" s="1">
-        <v>1</v>
-      </c>
-      <c r="M32" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>1</v>
-      </c>
-      <c r="N32" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>1</v>
+      </c>
+      <c r="L32" s="1">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>102</v>
       </c>
@@ -3292,33 +2758,29 @@
       <c r="E33" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="2">
+      <c r="G33" s="2">
         <v>0.70399999999999996</v>
       </c>
-      <c r="J33" s="3">
-        <v>1</v>
-      </c>
-      <c r="K33" s="1">
-        <v>1</v>
-      </c>
-      <c r="L33" s="1"/>
-      <c r="M33" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>1</v>
-      </c>
-      <c r="N33" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H33" s="3">
+        <v>1</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1</v>
+      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>1</v>
+      </c>
+      <c r="L33" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>103</v>
       </c>
@@ -3334,35 +2796,29 @@
       <c r="E34" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F34" t="s">
-        <v>220</v>
-      </c>
-      <c r="G34" t="s">
-        <v>220</v>
-      </c>
-      <c r="H34" s="3" t="s">
+      <c r="F34" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I34" s="4">
+      <c r="G34" s="4">
         <v>0.1085</v>
       </c>
-      <c r="J34" s="3">
-        <v>1</v>
-      </c>
-      <c r="K34" s="1">
-        <v>1</v>
-      </c>
-      <c r="L34" s="1"/>
-      <c r="M34" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>1</v>
-      </c>
-      <c r="N34" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H34" s="3">
+        <v>1</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1</v>
+      </c>
+      <c r="J34" s="1"/>
+      <c r="K34" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>1</v>
+      </c>
+      <c r="L34" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>104</v>
       </c>
@@ -3378,35 +2834,29 @@
       <c r="E35" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="F35" t="s">
-        <v>222</v>
-      </c>
-      <c r="G35" t="s">
-        <v>222</v>
-      </c>
-      <c r="H35" s="3" t="s">
+      <c r="F35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I35" s="4">
+      <c r="G35" s="4">
         <v>0.12189999999999999</v>
       </c>
-      <c r="J35" s="3">
-        <v>1</v>
-      </c>
-      <c r="K35" s="1">
-        <v>1</v>
-      </c>
-      <c r="L35" s="1"/>
-      <c r="M35" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>1</v>
-      </c>
-      <c r="N35" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H35" s="3">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1">
+        <v>1</v>
+      </c>
+      <c r="J35" s="1"/>
+      <c r="K35" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>1</v>
+      </c>
+      <c r="L35" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>105</v>
       </c>
@@ -3422,35 +2872,29 @@
       <c r="E36" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="G36" t="s">
-        <v>219</v>
-      </c>
-      <c r="H36" s="3" t="s">
+      <c r="F36" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I36" s="4">
+      <c r="G36" s="4">
         <v>0.37430000000000002</v>
       </c>
-      <c r="J36" s="3">
-        <v>1</v>
-      </c>
-      <c r="K36" s="1">
-        <v>1</v>
-      </c>
-      <c r="L36" s="1"/>
-      <c r="M36" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>1</v>
-      </c>
-      <c r="N36" s="3">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H36" s="3">
+        <v>1</v>
+      </c>
+      <c r="I36" s="1">
+        <v>1</v>
+      </c>
+      <c r="J36" s="1"/>
+      <c r="K36" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>1</v>
+      </c>
+      <c r="L36" s="3">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>106</v>
       </c>
@@ -3466,34 +2910,28 @@
       <c r="E37" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="G37" t="s">
-        <v>213</v>
-      </c>
-      <c r="H37" s="3" t="s">
+      <c r="F37" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="I37" s="4">
+      <c r="G37" s="4">
         <v>0.36480000000000001</v>
       </c>
-      <c r="J37" s="3">
+      <c r="H37" s="3">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1">
         <v>1</v>
       </c>
       <c r="K37" s="1">
-        <v>1</v>
-      </c>
-      <c r="M37" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>1</v>
-      </c>
-      <c r="N37" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>1</v>
+      </c>
+      <c r="L37" s="1">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>107</v>
       </c>
@@ -3509,43 +2947,43 @@
       <c r="E38" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I38" s="2">
+      <c r="G38" s="2">
         <v>0.8639</v>
       </c>
-      <c r="J38" s="1">
+      <c r="H38" s="1">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1">
         <v>1</v>
       </c>
       <c r="K38" s="1">
-        <v>1</v>
-      </c>
-      <c r="M38" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>1</v>
-      </c>
-      <c r="N38" s="1">
-        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
+        <v>1</v>
+      </c>
+      <c r="L38" s="1">
+        <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3">
         <f>COUNTA(Table1[Manf])</f>
         <v>34</v>
       </c>
-      <c r="J41" s="1">
+      <c r="H41" s="1">
         <f>SUM(Table1[Per Qty])</f>
         <v>69</v>
       </c>
-      <c r="M41" s="1">
+      <c r="K41" s="1">
         <f>SUM(Table1[Column1])</f>
         <v>57</v>
       </c>
-      <c r="N41" s="1">
+      <c r="L41" s="1">
         <f>SUM(Table1[Column2])</f>
         <v>12</v>
       </c>
@@ -3553,7 +2991,7 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A2:A38">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="DONE">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="DONE">
       <formula>NOT(ISERROR(SEARCH("DONE",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3569,446 +3007,4 @@
     </ext>
   </extLst>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECAE32E7-7895-42B0-B9C6-999EBEE1184D}">
-  <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="26.109375" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.109375" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D2" s="3" t="str">
-        <f>Table1[[#This Row],[Column5]]</f>
-        <v>C2907445</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D3" s="3" t="str">
-        <f>Table1[[#This Row],[Column5]]</f>
-        <v>C25379</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D4" s="3" t="str">
-        <f>Table1[[#This Row],[Column5]]</f>
-        <v>C17901</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D5" s="3" t="str">
-        <f>Table1[[#This Row],[Column5]]</f>
-        <v>C17887</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D6" s="3" t="str">
-        <f>Table1[[#This Row],[Column5]]</f>
-        <v>C2930433</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D7" s="3" t="str">
-        <f>Table1[[#This Row],[Column5]]</f>
-        <v>C17948</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D8" s="3" t="str">
-        <f>Table1[[#This Row],[Column5]]</f>
-        <v>C17902</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9" s="3" t="str">
-        <f>Table1[[#This Row],[Column5]]</f>
-        <v>C17927</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D11" s="3" t="str">
-        <f>Table1[[#This Row],[Column5]]</f>
-        <v>C142747</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D12" s="3" t="str">
-        <f>Table1[[#This Row],[Column5]]</f>
-        <v>C5137553</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D13" s="3" t="str">
-        <f>Table1[[#This Row],[Column5]]</f>
-        <v>C24497</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D14" s="3" t="str">
-        <f>Table1[[#This Row],[Column5]]</f>
-        <v>C1848</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D15" s="3" t="str">
-        <f>Table1[[#This Row],[Column5]]</f>
-        <v>C13585</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C17" t="s">
-        <v>198</v>
-      </c>
-      <c r="D17" s="1" t="str">
-        <f>Inclusive!F23</f>
-        <v>C5342990</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="1" t="str">
-        <f>Inclusive!F21</f>
-        <v>C91144</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="6"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D20" s="1" t="str">
-        <f>Inclusive!F27</f>
-        <v>C51680</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D21" s="1" t="str">
-        <f>Inclusive!F28</f>
-        <v>C69082</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D22" s="1" t="str">
-        <f>Inclusive!F29</f>
-        <v>C131974</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="1" t="str">
-        <f>Inclusive!F30</f>
-        <v>C2898686</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="1" t="str">
-        <f>Inclusive!F31</f>
-        <v>C50754</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D25" s="1" t="str">
-        <f>Inclusive!F32</f>
-        <v>C2860743</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D26" s="1" t="str">
-        <f>Inclusive!F33</f>
-        <v>C2984261</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D27" s="1" t="str">
-        <f>Inclusive!F34</f>
-        <v>C434442 </v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D28" s="1"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D29" s="1" t="str">
-        <f>Inclusive!F36</f>
-        <v>C5355897</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D30" s="1" t="str">
-        <f>Inclusive!F37</f>
-        <v>C962159</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A2:A30">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="DONE">
-      <formula>NOT(ISERROR(SEARCH("DONE",A2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EACDD468-810C-4EBE-B830-FE01E4A2676D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/hardware/devBoard/manufacture/devBoard BOM.xlsx
+++ b/hardware/devBoard/manufacture/devBoard BOM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Documents\GitHub\Embedded-Systems-Instructor\hardware\devBoard\manufacture\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\home.mines.edu\home\coulston\adit\My Documents\GitHub\Embedded-Systems-Instructor\hardware\devBoard\manufacture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A506DC-CA71-4A10-BD86-88E0336A8564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A699D83-4034-49E8-9452-025DCAC151E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="devBoard BOM" sheetId="4" r:id="rId1"/>
@@ -20,8 +20,19 @@
     <definedName name="distributors" localSheetId="0">'devBoard BOM'!$E$278</definedName>
     <definedName name="learn" localSheetId="0">'devBoard BOM'!$E$70</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -1602,20 +1613,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L41"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="26.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="1"/>
-    <col min="7" max="7" width="9.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.109375" style="1"/>
-    <col min="9" max="9" width="9.44140625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="2" width="26.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="1"/>
+    <col min="7" max="7" width="9.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.42578125" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>124</v>
       </c>
@@ -1651,7 +1662,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>80</v>
       </c>
@@ -1689,7 +1700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>81</v>
       </c>
@@ -1727,7 +1738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>82</v>
       </c>
@@ -1765,7 +1776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>83</v>
       </c>
@@ -1803,7 +1814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>84</v>
       </c>
@@ -1841,7 +1852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>85</v>
       </c>
@@ -1879,7 +1890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>86</v>
       </c>
@@ -1917,7 +1928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>87</v>
       </c>
@@ -1954,7 +1965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D10" s="1"/>
       <c r="G10" s="4"/>
       <c r="I10" s="1"/>
@@ -1968,7 +1979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>88</v>
       </c>
@@ -2006,7 +2017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>89</v>
       </c>
@@ -2043,7 +2054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>90</v>
       </c>
@@ -2066,7 +2077,7 @@
         <v>3.2719999999999999E-2</v>
       </c>
       <c r="H13" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
@@ -2074,14 +2085,14 @@
       <c r="J13" s="1"/>
       <c r="K13" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L13" s="3">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[Through]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>91</v>
       </c>
@@ -2119,7 +2130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>92</v>
       </c>
@@ -2157,7 +2168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K16" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>0</v>
@@ -2167,7 +2178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>125</v>
       </c>
@@ -2205,7 +2216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>126</v>
       </c>
@@ -2243,7 +2254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>128</v>
       </c>
@@ -2281,7 +2292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>93</v>
       </c>
@@ -2319,7 +2330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>94</v>
       </c>
@@ -2357,7 +2368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>95</v>
       </c>
@@ -2395,7 +2406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>110</v>
       </c>
@@ -2433,7 +2444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>96</v>
       </c>
@@ -2471,7 +2482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>97</v>
       </c>
@@ -2508,7 +2519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K26" s="1">
         <f>Table1[[#This Row],[Per Qty]]*Table1[[#This Row],[SMT]]</f>
         <v>0</v>
@@ -2518,7 +2529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>177</v>
       </c>
@@ -2555,7 +2566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>98</v>
       </c>
@@ -2593,7 +2604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>99</v>
       </c>
@@ -2631,7 +2642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>100</v>
       </c>
@@ -2668,7 +2679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>117</v>
       </c>
@@ -2705,7 +2716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>101</v>
       </c>
@@ -2742,7 +2753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>102</v>
       </c>
@@ -2780,7 +2791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>103</v>
       </c>
@@ -2818,7 +2829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>104</v>
       </c>
@@ -2856,7 +2867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>105</v>
       </c>
@@ -2894,7 +2905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>106</v>
       </c>
@@ -2931,7 +2942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>107</v>
       </c>
@@ -2968,7 +2979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3">
@@ -2977,11 +2988,11 @@
       </c>
       <c r="H41" s="1">
         <f>SUM(Table1[Per Qty])</f>
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K41" s="1">
         <f>SUM(Table1[Column1])</f>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L41" s="1">
         <f>SUM(Table1[Column2])</f>
